--- a/Result/profitability/3646.xlsx
+++ b/Result/profitability/3646.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07625000000000001</v>
+        <v>0.007500000000000007</v>
       </c>
       <c r="N2" t="n">
-        <v>26.5725</v>
+        <v>25.87125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04625000000000001</v>
+        <v>0.03125000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>23.93375</v>
+        <v>23.57</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.76</v>
       </c>
       <c r="M4" t="n">
-        <v>0.135</v>
+        <v>0.12125</v>
       </c>
       <c r="N4" t="n">
-        <v>23.5725</v>
+        <v>23.47375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.54</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1975</v>
+        <v>0.13125</v>
       </c>
       <c r="N5" t="n">
-        <v>23.85375</v>
+        <v>23.2525</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>0.17375</v>
+        <v>0.15875</v>
       </c>
       <c r="N6" t="n">
-        <v>22.29125</v>
+        <v>21.8675</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.27</v>
       </c>
       <c r="M7" t="n">
-        <v>0.32625</v>
+        <v>0.31625</v>
       </c>
       <c r="N7" t="n">
-        <v>18.5925</v>
+        <v>18.0875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>0.335</v>
+        <v>0.37125</v>
       </c>
       <c r="N8" t="n">
-        <v>21.4125</v>
+        <v>21.54875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9195,6 +9195,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3646</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>216</v>
+      </c>
+      <c r="D70" t="n">
+        <v>162</v>
+      </c>
+      <c r="E70" t="n">
+        <v>53</v>
+      </c>
+      <c r="F70" t="n">
+        <v>24.73</v>
+      </c>
+      <c r="G70" t="n">
+        <v>7</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="N70" t="n">
+        <v>27.2875</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="X70" t="n">
+        <v>-0.8055555555555556</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.04610829103214886</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>-1.152173913043478</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>-4.809999999999999</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>-0.1628300609343263</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
